--- a/GameDesign/Excel/EquipEnchant.xlsx
+++ b/GameDesign/Excel/EquipEnchant.xlsx
@@ -473,7 +473,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -688,7 +688,7 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>OptionTID</t>
+          <t>EnchantOptionTID</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">

--- a/GameDesign/Excel/EquipEnchant.xlsx
+++ b/GameDesign/Excel/EquipEnchant.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,11 +725,11 @@
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="6" t="n">
-        <v>101</v>
+        <v>1101</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -743,25 +743,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>300</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>전 산업 +2%</t>
+          <t>일반 전 산업 +0.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="6" t="n">
-        <v>102</v>
+        <v>1102</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -775,25 +775,25 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>농사 +4%</t>
+          <t>일반 농사 +1%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="6" t="n">
-        <v>103</v>
+        <v>1103</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -807,25 +807,25 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>낚시 +4%</t>
+          <t>일반 낚시 +1%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="6" t="n">
-        <v>104</v>
+        <v>1104</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>채굴 +4%</t>
+          <t>일반 채굴 +1%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="6" t="n">
-        <v>105</v>
+        <v>1105</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>벌목 +4%</t>
+          <t>일반 벌목 +1%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="6" t="n">
-        <v>106</v>
+        <v>1106</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>사냥 +4%</t>
+          <t>일반 사냥 +1%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="6" t="n">
-        <v>107</v>
+        <v>1107</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -935,25 +935,25 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>100</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>경험치 +3%</t>
+          <t>일반 경험치 +1%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="6" t="n">
-        <v>201</v>
+        <v>1201</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>300</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>전 산업 +5%</t>
+          <t>고급 전 산업 +1%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="6" t="n">
-        <v>202</v>
+        <v>1202</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -999,25 +999,25 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>농사 +9%</t>
+          <t>고급 농사 +2%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="6" t="n">
-        <v>203</v>
+        <v>1203</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1031,25 +1031,25 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>낚시 +9%</t>
+          <t>고급 낚시 +2%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="6" t="n">
-        <v>204</v>
+        <v>1204</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1063,25 +1063,25 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>채굴 +9%</t>
+          <t>고급 채굴 +2%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="6" t="n">
-        <v>205</v>
+        <v>1205</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1095,25 +1095,25 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>벌목 +9%</t>
+          <t>고급 벌목 +2%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="6" t="n">
-        <v>206</v>
+        <v>1206</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1127,25 +1127,25 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>사냥 +9%</t>
+          <t>고급 사냥 +2%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="6" t="n">
-        <v>207</v>
+        <v>1207</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1159,25 +1159,25 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>100</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>경험치 +7%</t>
+          <t>고급 경험치 +2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="6" t="n">
-        <v>301</v>
+        <v>1301</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1191,25 +1191,25 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>300</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>전 산업 +10%</t>
+          <t>희귀 전 산업 +2%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="6" t="n">
-        <v>302</v>
+        <v>1302</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1223,25 +1223,25 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>농사 +18%</t>
+          <t>희귀 농사 +4%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="6" t="n">
-        <v>303</v>
+        <v>1303</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1255,25 +1255,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>낚시 +18%</t>
+          <t>희귀 낚시 +4%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="6" t="n">
-        <v>304</v>
+        <v>1304</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>채굴 +18%</t>
+          <t>희귀 채굴 +4%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="6" t="n">
-        <v>305</v>
+        <v>1305</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1319,25 +1319,25 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>벌목 +18%</t>
+          <t>희귀 벌목 +4%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="6" t="n">
-        <v>306</v>
+        <v>1306</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1351,25 +1351,25 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>120</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>사냥 +18%</t>
+          <t>희귀 사냥 +4%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="6" t="n">
-        <v>307</v>
+        <v>1307</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1383,14 +1383,686 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>100</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>경험치 +15%</t>
+          <t>희귀 경험치 +3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>영웅 전 산업 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="6" t="n">
+        <v>1402</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>영웅 농사 +9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="6" t="n">
+        <v>1403</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>영웅 낚시 +9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="6" t="n">
+        <v>1404</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>영웅 채굴 +9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="6" t="n">
+        <v>1405</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>영웅 벌목 +9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="6" t="n">
+        <v>1406</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>영웅 사냥 +9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="6" t="n">
+        <v>1407</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>CharacterExp</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>영웅 경험치 +7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="6" t="n">
+        <v>1501</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>전설 전 산업 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="6" t="n">
+        <v>1502</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>전설 농사 +18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>전설 낚시 +18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="6" t="n">
+        <v>1504</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>전설 채굴 +18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="6" t="n">
+        <v>1505</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>전설 벌목 +18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="6" t="n">
+        <v>1506</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>전설 사냥 +18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="6" t="n">
+        <v>1507</v>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>CharacterExp</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>전설 경험치 +15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="6" t="n">
+        <v>1601</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>신화 전 산업 +14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="6" t="n">
+        <v>1602</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>신화 농사 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="6" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>신화 낚시 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="6" t="n">
+        <v>1604</v>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>신화 채굴 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="6" t="n">
+        <v>1605</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>신화 벌목 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="6" t="n">
+        <v>1606</v>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>신화 사냥 +25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="6" t="n">
+        <v>1607</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>CharacterExp</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>신화 경험치 +20%</t>
         </is>
       </c>
     </row>
@@ -1405,13 +2077,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1419,6 +2092,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1433,10 +2107,15 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>상승 확률(‰)</t>
+          <t>칸 수</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>상승 확률(‱)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1463,6 +2142,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1481,6 +2165,11 @@
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1496,7 +2185,10 @@
       <c r="C5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1506,9 +2198,12 @@
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1518,7 +2213,8 @@
       </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1533,6 +2229,7 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -1543,10 +2240,15 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>UpPermille</t>
+          <t>SlotCount</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>UpPermyriad</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1556,15 +2258,18 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>→ Epic 5%</t>
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>일반 장비 1칸 · 큐브 A → 고급 16%</t>
         </is>
       </c>
     </row>
@@ -1572,15 +2277,18 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>→ Legendary 0.5%</t>
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>고급 장비 1칸 · 큐브 A → 희귀 8%</t>
         </is>
       </c>
     </row>
@@ -1588,15 +2296,75 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="7" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>희귀 장비 2칸 · 큐브 A → 영웅 4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>영웅 장비 2칸 · 큐브 A → 전설 0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>전설 장비 3칸 · 큐브 A → 신화 0.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>최고 등급 — 재롤만</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>신화 장비 3칸 · 큐브 A 최고 등급 — 옵션만 다시 뽑는다</t>
         </is>
       </c>
     </row>
@@ -1611,13 +2379,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1626,7 +2394,6 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1641,15 +2408,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>동작</t>
+          <t>상승 배율(‰)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>성공 확률(‰)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1676,11 +2438,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1695,15 +2452,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>eEnchantAction</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1718,11 +2470,10 @@
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1732,10 +2483,7 @@
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1745,8 +2493,7 @@
       </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1765,7 +2512,6 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -1776,15 +2522,10 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>UpRatePermille</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>SuccessPermille</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1793,95 +2534,28 @@
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="6" t="n">
-        <v>100013</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>인챈트 원석 — 50% 부여</t>
+        <v>100015</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 — 기본 상승 확률</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="6" t="n">
-        <v>100014</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>정제된 인챈트 원석 — 확정 부여</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="6" t="n">
-        <v>100015</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>GradeUp</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>인챈트 큐브 — 이 값은 읽지 않는다. 상승 확률은 EnchantGradeTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="6" t="n">
-        <v>100016</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>ExpandLine</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>인챈트 확장석 — 30% 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="6" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>ExpandLine</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>정제된 인챈트 확장석 — 확정 확장</t>
+        <v>100018</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 — 상승 확률 ×1.25</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/EquipEnchant.xlsx
+++ b/GameDesign/Excel/EquipEnchant.xlsx
@@ -2379,14 +2379,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2394,6 +2394,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2413,6 +2414,11 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>이전 값 유지</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -2438,6 +2444,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2457,6 +2468,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -2474,6 +2490,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2484,6 +2501,7 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2493,7 +2511,8 @@
       </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2512,6 +2531,7 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -2526,6 +2546,11 @@
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CanKeepPrevious</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2539,7 +2564,10 @@
       <c r="C10" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>인챈트 큐브 — 기본 상승 확률</t>
         </is>
@@ -2553,7 +2581,10 @@
       <c r="C11" s="6" t="n">
         <v>1250</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>상급 인챈트 큐브 — 상승 확률 ×1.25</t>
         </is>

--- a/GameDesign/Excel/EquipEnchant.xlsx
+++ b/GameDesign/Excel/EquipEnchant.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>일반 낚시 +1%</t>
+          <t>일반 발굴 +1%</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>고급 낚시 +2%</t>
+          <t>고급 발굴 +2%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>희귀 낚시 +4%</t>
+          <t>희귀 발굴 +4%</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>영웅 낚시 +9%</t>
+          <t>영웅 발굴 +9%</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>전설 낚시 +18%</t>
+          <t>전설 발굴 +18%</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>신화 낚시 +25%</t>
+          <t>신화 발굴 +25%</t>
         </is>
       </c>
     </row>
